--- a/case_studies/base_case/2050/technologies.xlsx
+++ b/case_studies/base_case/2050/technologies.xlsx
@@ -691,31 +691,31 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0</v>
+        <v>55.45</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>109.95</v>
+        <v>353.04</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0</v>
+        <v>24.96</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>48.18</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>135.49</v>
+        <v>114.38</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>184.21</v>
+        <v>163.1</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>22.37</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>39.34</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>117.93</v>
+        <v>240.36</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -888,13 +888,13 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>143.64</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>81.48999999999999</v>
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>203.26</v>
+        <v>93.92</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>247.76</v>
+        <v>156.42</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0</v>
+        <v>143.41</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>43.32</v>
@@ -927,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0</v>
+        <v>144.41</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.51</v>
+        <v>30.06</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -973,40 +973,40 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>28.15</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>198.79</v>
+        <v>257.29</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2.59</v>
+        <v>52.56</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>20.79</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>46.87</v>
+        <v>39.94</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>39.94</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
@@ -1079,16 +1079,16 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>51.37</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>156.18</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>141.94</v>
+        <v>179.81</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>141.93</v>
+        <v>179.81</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0</v>
+        <v>99.73</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0</v>
@@ -1121,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0</v>
+        <v>99.73</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>395.23</v>
+        <v>361.56</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>19.67</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>29.92</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>38.81</v>
+        <v>24</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1209,13 +1209,13 @@
         <v>0</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>29.92</v>
+        <v>19.67</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W7" s="5" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>108.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>158.68</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>157.86</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -1294,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>265.9</v>
+        <v>166.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>280.87</v>
+        <v>219.24</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>9.859999999999999</v>
+        <v>35.73</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>79.56</v>
+        <v>42.85</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>1.88</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0</v>
+        <v>44.74</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>136.33</v>

--- a/case_studies/base_case/2050/technologies.xlsx
+++ b/case_studies/base_case/2050/technologies.xlsx
@@ -691,52 +691,52 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>55.45</v>
+        <v>116.03</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>353.04</v>
+        <v>476.25</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>11.38</v>
+        <v>946.41</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>11.38</v>
+        <v>946.41</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>114.38</v>
+        <v>231.24</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>163.1</v>
+        <v>257.06</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>22.37</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>1.92</v>
+        <v>159.94</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>39.34</v>
+        <v>49.16</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>240.36</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>0</v>
+        <v>686.54</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0</v>
+        <v>45.66</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>3.55</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0</v>
+        <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0</v>
+        <v>32.33</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>0</v>
@@ -836,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>0</v>
+        <v>44.45</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>39.95</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -879,46 +879,46 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>177.64</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>143.64</v>
+        <v>515</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0</v>
+        <v>1369.36</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0</v>
+        <v>1369.36</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>93.92</v>
+        <v>507.32</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>156.42</v>
+        <v>539.04</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>143.41</v>
+        <v>196.77</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>43.32</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -927,16 +927,16 @@
         <v>0</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>144.41</v>
+        <v>196.77</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>30.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>27.91</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -976,37 +976,37 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>28.15</v>
+        <v>108.7</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>257.29</v>
+        <v>449.02</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>52.56</v>
+        <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>23.95</v>
+        <v>745.4</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>23.95</v>
+        <v>745.4</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>39.94</v>
+        <v>122.67</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>39.94</v>
+        <v>122.67</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>4.04</v>
+        <v>125.97</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
@@ -1027,13 +1027,13 @@
         <v>189.3</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>643.22</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>0</v>
+        <v>204.22</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>51.37</v>
+        <v>61.1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>156.18</v>
+        <v>221.12</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1091,28 +1091,28 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0</v>
+        <v>565.33</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>179.81</v>
+        <v>204.43</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>179.81</v>
+        <v>204.43</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>99.73</v>
+        <v>106.41</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1121,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>99.73</v>
+        <v>106.41</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>361.56</v>
+        <v>242.76</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>19.67</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>3.11</v>
+        <v>59.3</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -1197,28 +1197,28 @@
         <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>24</v>
+        <v>97.03</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>0</v>
+        <v>19.82</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>0</v>
+        <v>15.67</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>19.67</v>
+        <v>48.52</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0</v>
+        <v>19.43</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>108.4</v>
+        <v>119.69</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>158.68</v>
+        <v>327.09</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,40 +1285,40 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>653.27</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0</v>
+        <v>653.27</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>166.26</v>
+        <v>239.37</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>219.24</v>
+        <v>323.79</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>108.99</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>35.73</v>
+        <v>73.62</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.85</v>
+        <v>119.69</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>44.74</v>
+        <v>146.57</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>136.33</v>
+        <v>261.31</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
